--- a/data/chinese/P2T3_Chapter19.xlsx
+++ b/data/chinese/P2T3_Chapter19.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/單詞複習網素材/Chinese/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/homes/ximonlam/Mac/單詞複習網素材/Chinese/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7463E039-E47A-0245-A03A-8B9E71F27225}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A900A7C-5A99-784C-9F76-D71FB8B922F1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -60,145 +60,161 @@
     <t>盛開</t>
   </si>
   <si>
-    <t>花朵開得又多又美</t>
-  </si>
-  <si>
     <t>春天花園裡的牡丹全都盛開了。</t>
   </si>
   <si>
     <t>幸福</t>
   </si>
   <si>
-    <t>內心滿足快樂、安愉的感受</t>
-  </si>
-  <si>
     <t>和家人相處在一起，我覺得十分幸福。</t>
   </si>
   <si>
     <t>喧鬧</t>
   </si>
   <si>
-    <t>聲音嘈雜、熱鬧吵雜</t>
-  </si>
-  <si>
     <t>放學後的校門口十分喧鬧。</t>
   </si>
   <si>
     <t>允許</t>
   </si>
   <si>
-    <t>准許、同意別人做某事</t>
-  </si>
-  <si>
     <t>媽媽允許我週末到公園遊玩。</t>
   </si>
   <si>
     <t>孤獨</t>
   </si>
   <si>
-    <t>獨自一人，內心寂寞無伴</t>
-  </si>
-  <si>
     <t>身邊沒有夥伴時，他感到很孤獨。</t>
   </si>
   <si>
     <t>凝視</t>
   </si>
   <si>
-    <t>專心、久久地盯著看</t>
-  </si>
-  <si>
     <t>他站在窗前，凝視遠方的夕陽。</t>
   </si>
   <si>
     <t>明媚</t>
   </si>
   <si>
-    <t>光線亮麗柔和，多用來形容陽光、春光</t>
-  </si>
-  <si>
     <t>今天陽光明媚，適合出外踏青。</t>
   </si>
   <si>
     <t>訓斥</t>
   </si>
   <si>
-    <t>嚴厲地責備、斥罵</t>
-  </si>
-  <si>
     <t>因為隨意損壞花草，他被爺爺訓斥了一頓。</t>
   </si>
   <si>
     <t>洋溢</t>
   </si>
   <si>
-    <t>情緒、氣氛充分顯現、滿滿散開</t>
-  </si>
-  <si>
     <t>整間屋子裡洋溢著歡樂的氣息。</t>
   </si>
   <si>
     <t>荒涼</t>
   </si>
   <si>
-    <t>人煙稀少、冷清蕭索</t>
-  </si>
-  <si>
     <t>秋冬到來，無人打理的庭院變得十分荒涼。</t>
   </si>
   <si>
     <t>逃散</t>
   </si>
   <si>
-    <t>受驚後各自跑開、四散躲避</t>
-  </si>
-  <si>
     <t>聽到巨響，鳥兒們立刻往各處逃散。</t>
   </si>
   <si>
     <t>鮮花凋謝</t>
   </si>
   <si>
-    <t>花朵枯萎、落下，不再盛開</t>
-  </si>
-  <si>
     <t>秋風吹過，園中鮮花凋謝，滿地落瓣。</t>
   </si>
   <si>
     <t>瑟瑟發抖</t>
   </si>
   <si>
-    <t>因寒冷、害怕而身體不停顫動</t>
-  </si>
-  <si>
     <t>屋外寒風刺骨，他凍得瑟瑟發抖。</t>
   </si>
   <si>
     <t>北風呼嘯</t>
   </si>
   <si>
-    <t>寒冷的北風猛烈吹動，發出巨大響聲</t>
-  </si>
-  <si>
     <t>冬夜北風呼嘯，窗戶被吹得砰砰作響。</t>
   </si>
   <si>
     <t>狂風大作</t>
   </si>
   <si>
-    <t>颳起極大的風，風勢猛烈</t>
-  </si>
-  <si>
     <t>午後忽然狂風大作，路人紛紛找地方躲避。</t>
   </si>
   <si>
     <t>四處逃散</t>
   </si>
   <si>
-    <t>受驚後往各個方向分散逃跑</t>
-  </si>
-  <si>
     <t>野獸看見獵人，立刻四處逃散。</t>
+  </si>
+  <si>
+    <t>花開得又大又漂亮，全部展開的樣子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>感覺很快樂、很滿足，心裡暖暖的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>聲音很多、很吵雜，熱鬧又嘈雜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同意、准許別人做某件事</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一個人，沒有同伴，覺得寂寞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>專心、一直看著某個東西，不移開視線</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>形容陽光很亮、景色很美好</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>嚴厲地責罵、批評</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>充滿、散發出來，比如臉上洋溢著笑容</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>地方沒有人、沒有東西，冷冷清清的樣子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>因為害怕而到處跑開、分散開</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>花開過後慢慢枯萎、落下來</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>因為冷或害怕而不停發抖</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冬天的北風很大，吹得呼呼響</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>突然颳起很大的風，天氣變得很壞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>向各個方向跑開，躲起來</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -877,7 +893,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26.83203125" customWidth="1"/>
-    <col min="2" max="2" width="53.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="68.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="71.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="39.83203125" bestFit="1" customWidth="1"/>
@@ -912,10 +928,10 @@
         <v>7</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>9</v>
       </c>
       <c r="D2" s="3">
         <v>1</v>
@@ -924,13 +940,13 @@
     </row>
     <row r="3" spans="1:11" ht="27">
       <c r="A3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>12</v>
       </c>
       <c r="D3" s="3">
         <v>1</v>
@@ -939,13 +955,13 @@
     </row>
     <row r="4" spans="1:11" ht="27">
       <c r="A4" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D4" s="3">
         <v>1</v>
@@ -954,13 +970,13 @@
     </row>
     <row r="5" spans="1:11" ht="27">
       <c r="A5" s="3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D5" s="3">
         <v>1</v>
@@ -969,13 +985,13 @@
     </row>
     <row r="6" spans="1:11" ht="27">
       <c r="A6" s="3" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D6" s="3">
         <v>2</v>
@@ -984,13 +1000,13 @@
     </row>
     <row r="7" spans="1:11" ht="27">
       <c r="A7" s="3" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D7" s="3">
         <v>2</v>
@@ -999,13 +1015,13 @@
     </row>
     <row r="8" spans="1:11" ht="27">
       <c r="A8" s="3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D8" s="3">
         <v>2</v>
@@ -1014,13 +1030,13 @@
     </row>
     <row r="9" spans="1:11" ht="27">
       <c r="A9" s="3" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D9" s="3">
         <v>2</v>
@@ -1029,13 +1045,13 @@
     </row>
     <row r="10" spans="1:11" ht="27">
       <c r="A10" s="3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D10" s="3">
         <v>3</v>
@@ -1044,13 +1060,13 @@
     </row>
     <row r="11" spans="1:11" ht="27">
       <c r="A11" s="3" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="D11" s="3">
         <v>3</v>
@@ -1059,13 +1075,13 @@
     </row>
     <row r="12" spans="1:11" ht="27">
       <c r="A12" s="3" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="D12" s="3">
         <v>3</v>
@@ -1074,13 +1090,13 @@
     </row>
     <row r="13" spans="1:11" ht="27">
       <c r="A13" s="3" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="D13" s="3">
         <v>3</v>
@@ -1089,13 +1105,13 @@
     </row>
     <row r="14" spans="1:11" ht="27">
       <c r="A14" s="3" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="D14" s="3">
         <v>4</v>
@@ -1104,13 +1120,13 @@
     </row>
     <row r="15" spans="1:11" ht="27">
       <c r="A15" s="3" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="D15" s="3">
         <v>4</v>
@@ -1119,13 +1135,13 @@
     </row>
     <row r="16" spans="1:11" ht="27">
       <c r="A16" s="3" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="D16" s="3">
         <v>4</v>
@@ -1134,13 +1150,13 @@
     </row>
     <row r="17" spans="1:6" ht="27">
       <c r="A17" s="3" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="D17" s="3">
         <v>4</v>
